--- a/Result/checksun_type/塑膠_金屬機殼.xlsx
+++ b/Result/checksun_type/塑膠_金屬機殼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2767</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2040</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7527</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2843</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>8850</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4645</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2921</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6307</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>20919</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>13648</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>9458</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>13919</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>14252</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>34781</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4464</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>14.83</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>14.49</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14.49</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1369.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1299.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1299.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2410.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1305.72</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1305.72</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-16.72278206297756</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1369</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1369.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>14.81</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>14.29</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>303.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1765.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1765</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2315.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1331.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1331.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>12.82491860009418</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>303</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>303.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2055.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1969.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1969</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2328.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1357.08</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1357.08</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>168.792172454479</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2055</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2055.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>14.26</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1194.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2314.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2314.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2190.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1405.28</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1405.28</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>197.8599575159396</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1194</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1194.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1577.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3742.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3742.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>2118.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1449.38</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1449.38</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>324.568937692457</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1577</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1577.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>14.65</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>14.49</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>14.49</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3696.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>3520.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>3520.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>2025.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1460.92</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1460.92</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>452.954304455609</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3696</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3696.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>14.46</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>14.5</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1323.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>2865.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>2865.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1795.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1452.46</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1452.46</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>393.1493175295543</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1323</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1323.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>14.3</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>14.51</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.51</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>3781.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>2688.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>2688</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1719.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1496.38</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1496.38</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>547.9225748662773</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>3781</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>3781.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>14.12</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>14.52</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>8336.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>2066.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>2066.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1399.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1502.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1502.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>486.1014219592291</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>8336</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>8336.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>13.85</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>14.18</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>14.53</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>14.53</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>467.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>495.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>495.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>687.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1487.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1487.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-107.6109901208119</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>467</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>467.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>13.85</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>14.19</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>14.58</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>419.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>530.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>530.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>705.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1737.58</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1737.58</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-108.8211863022702</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>419</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>419.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>276.7</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>286.85</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>283.97</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>286.85</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>283.97</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>965049243.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>614397649.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>614397649</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>655347732.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>822512332.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>822512332.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-78047471.70905769</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>965049243</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>965049243.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>272.2</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>286.8</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>283.62</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>283.62</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>436874814.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>522184324.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>522184324.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>745283070.8</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>821220532.6</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>821220532.6</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-114148617.9951471</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>436874814</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>436874814.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>271.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>286.77</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>283.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>286.77</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>283.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>375423288.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>581170929.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>581170929.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>803077159.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>825501453.94</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>825501453.9400001</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-105054830.3683053</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>375423288</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>375423288.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>274.5</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>287.1</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>284.28</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>284.28</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>760469412.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>644040988.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>644040988.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>887703605.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>826201621.38</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>826201621.38</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-81727654.88823485</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>760469412</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>760469412.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>280.9</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>287.4</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>284.93</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>284.93</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>534171488.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>604961462.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>604961462.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1010937520.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>827798392.18</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>827798392.1799999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-86739215.52784002</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>534171488</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>534171488.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>284.8</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>286.88</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>285.25</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>286.88</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>285.25</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>503982619.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>696297815.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>696297815.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1150951209.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>833460546.46</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>833460546.46</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-66554552.60128164</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>503982619</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>503982619.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>290.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>287.12</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>285.8</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>287.12</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>285.8</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>731807841.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>968381817.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>968381817.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1296224781.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>866499575.78</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>866499575.78</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-32107849.86329532</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>731807841</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>731807841.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>292.1</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>287.12</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>286.31</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>287.12</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>286.31</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>689773582.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1024983390.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1024983390.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1307084233.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>889751348.9</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>889751348.9</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-6161410.813911438</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>689773582</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>689773582.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>290.3</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>286.6</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>286.51</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>286.51</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>565071784.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1131366222.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1131366222.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1377042545.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>924065042.7</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>924065042.7</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>35628651.6785624</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>565071784</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>565071784.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>290.4</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>285.92</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>286.23</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>285.92</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>286.23</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>990853250.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1416913577.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1416913577.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1512952151.7</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>942245118.2</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>942245118.2</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>107417196.0364335</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>990853250</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>990853250.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>289.7</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>284.82</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>285.69</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>284.82</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>285.69</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1864402630.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1605604603.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1605604603.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1504827726.4</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>940578735.14</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>940578735.14</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>160516488.1892335</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1864402630</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1864402630.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>4839409.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>4150623.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>4150623.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>12016844.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>5000620.36</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>5000620.36</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-474302.7901694858</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>4839409</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>4839409.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>13.17</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>13.32</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>13.32</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3462528.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>5124985.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>5124985.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>11912618.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>5005524.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>5005524.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-254126.6060248017</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3462528</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3462528.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>13.28</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>13.33</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>13.33</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2803781.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>7422261.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>7422261.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>11835459.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>4995745.04</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>4995745.04</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>217009.7143970616</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2803781</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2803781.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>13.52</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>12.93</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>13.36</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>13.36</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>5283819.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>17030232.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>17030232.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>11728295.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>4959750.22</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>4959750.22</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>952891.2894855421</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>5283819</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>5283819.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>13.66</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>12.98</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>13.38</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>13.38</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>4363579.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>20252690.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>20252690</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>11505390.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>4908787.98</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>4908787.98</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1704400.493558887</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>4363579</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>4363579.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>13.4</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>9711222.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>19883066.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>19883066.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>11413173.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>4897762.86</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>4897762.86</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>2815710.767465135</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>9711222</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>9711222.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>13.27</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>13.03</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>13.41</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>13.41</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>14948905.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>18700251.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>18700251.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>10986656.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>4722230.96</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>4722230.96</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>3729774.024207447</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>14948905</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>14948905.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>12.93</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>13.41</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>13.41</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>50843636.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>16248657.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>16248657.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>10468393.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>4455630.14</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>4455630.14</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>4341192.140117627</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>50843636</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>50843636.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>12.56</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>12.97</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>13.4</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>21396108.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>6426357.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>6426357.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>6167061.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>3510123.28</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>3510123.28</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>1213739.979270825</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>21396108</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>21396108.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>12.33</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>12.96</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>13.42</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2515461.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2758091.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2758091.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4481247.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>3136689.58</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>3136689.58</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-142304.3926271345</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2515461</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2515461.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>12.31</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>13.46</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>13.46</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>3797146.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>2943281.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>2943281.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4739424.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>3198856.32</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>3198856.32</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-51501.87417325005</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>3797146</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>3797146.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>38.29000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>39.8</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>43.53</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>73681.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>42181.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>42181.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>77212.2</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>145670.48</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>145670.48</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-8764.904842059172</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>73681</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>73681.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>37.91</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>39.92</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>43.76</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>43.76</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>31026.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>34517.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>34517.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>86282.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>158266.12</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>158266.12</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-11675.0456811521</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>31026</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>31026.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>37.73999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>44.01</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>44.01</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>40112.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>39364.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>39364</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>87113.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>162395.06</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>162395.06</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-10845.24524838656</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>40112</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>40112.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>38.09</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>44.29</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>28528.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>41508.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>41508.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>86793.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>170730.44</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>170730.44</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-10245.98587127912</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>28528</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>28528.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>38.6</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>44.62</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>37561.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>57338.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>57338.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>89033.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>179785.32</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>179785.32</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-7782.830122865678</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>37561</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>37561.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>39.14</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>40.91</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>44.95</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>35360.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>112242.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>112242.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>90580.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>190231.08</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>190231.08</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-4953.899406458411</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>35360</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>35360.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>40.3</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>41.22</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>45.33</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>45.33</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>55259.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>138048.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>138048</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>94362.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>214493.36</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>214493.36</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-499.8234042173572</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>55259</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>55259.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>40.57</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>41.44</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>45.75</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>50835.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>134862.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>134862</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>97142.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>269944.92</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>269944.92</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>3748.957434849042</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>50835</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>50835.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>40.57</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>41.59</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>46.1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>107677.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>132078.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>132078.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>96602.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>390988.38</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>390988.38</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>10158.75301084215</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>107677</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>107677.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>40.64</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>41.84</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>46.42</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>46.42</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>312083.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>120727.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>120727.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>89340.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>434310.68</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>434310.68</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>12862.57694044507</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>312083</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>312083.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>40.57000000000001</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>46.6</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>46.6</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>164386.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>68918.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>68918.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>63027.8</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>436239.4</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>436239.4</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-5634.838050852355</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>164386</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>164386.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>42.16</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>45.07</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>7608.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>12790.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>12790.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>22894.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>0</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-7965.063632370584</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>7608</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>7608.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>45.32</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>44.35</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>9618.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>16170.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>16170.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>24583.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>0</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-7834.864888357792</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>9618</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>9618.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>42.12</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>45.53</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>44.31</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>44.31</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>6289.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>19897.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>19897.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>31354.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>0</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-7584.407222326743</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>6289</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>6289.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>42.68</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>45.89</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>44.3</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>21866.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>23521.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>23521.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>35641.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>0</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-6599.060298627861</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>21866</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>21866.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>43.4</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>46.38</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>44.27</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>44.27</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>18572.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>25142.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>25142.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>40110.5</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>0</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-6624.705396964178</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>18572</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>18572.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>43.75</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>44.21</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>44.21</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>24508.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>32997.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>32997.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>41375.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>0</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-6071.816058981625</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>24508</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>24508.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>44.63</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>44.17</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>44.17</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>28252.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>32996.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>32996.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>41302.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>0</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-5701.123574042911</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>28252</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>28252.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>45.27</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>47.62</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>44.08</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>44.08</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>24408.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>42811.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>42811.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>40869.3</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>0</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-5369.094182200366</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>24408</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>24408.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>45.91</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>43.93</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>43.93</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>29972.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>47761.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>47761.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>40759.8</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>0</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-4291.155973060995</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>29972</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>29972.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>46.57000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>48.24</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>43.77</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>43.77</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>57849.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>55078.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>55078.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>38952.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>0</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-3194.13153239544</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>57849</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>57849.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>47.05</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>43.6</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>24500.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>49752.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>49752.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>36608.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>0</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-4499.699062430525</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>24500</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>24500.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>27.42</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>27.09</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>27.09</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>284.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>243.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>243.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>194.4</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>424.76</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>424.76</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-15.00604647618442</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>284</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>284.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>27.26</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>27.71</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>27.01</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>27.01</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>250.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>251.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>251.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>184.3</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>420.76</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>420.76</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-21.12522363249201</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>250</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>27.19</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>26.96</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>26.96</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>392.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>227.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>227.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>171.4</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>426.06</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>426.06</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-25.46957586891384</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>392</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>392.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>27.15</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>26.92</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>26.92</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>167.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>155.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>155.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>161.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>419.84</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>419.84</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-45.9804513541981</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>167</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>124.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>145.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>145.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>418.2</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>418.2</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-49.53240021338286</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>124</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>27.37</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>26.85</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>323.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>145.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>145.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>175.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>431.28</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>431.28</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-48.23045571888309</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>323</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>323.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>27.46</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>26.81</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>26.81</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>133.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>117.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>117.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>289.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>438.46</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>438.46</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-65.96944730820908</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>133</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>27.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>26.77</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>26.77</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>31.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>115</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>303.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>465.08</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>465.08</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-68.59766931766725</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>31</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>27.51</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>27.62</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>26.75</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>26.75</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>167.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>167.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>349.2</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>482.36</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>482.36</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-58.97378399840511</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>118</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>27.65</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>27.57</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>26.76</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>26.76</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>147.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>397.3</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>495.54</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>495.54</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-52.44059839951615</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>122</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>27.69</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>26.77</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>26.77</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>183.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>205.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>205.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>477.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>507.8</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>507.8</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-41.66316902969203</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>183</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>183.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39239,11 +38711,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>2476</t>
@@ -39425,41 +38893,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT90" t="inlineStr">
         <is>
           <t>0</t>
@@ -39480,20 +38944,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>0</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>0</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>0</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39675,11 +39137,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>2459</t>
@@ -39861,41 +39319,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO91" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr">
         <is>
           <t>0</t>
@@ -39916,20 +39370,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>0</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>0</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39396,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>0</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39565,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39749,11 @@
           <t>15.77</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>16.9</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39800,16 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>2276.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>2276.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>2169.6</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>2929.94</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>2929.94</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39826,10 @@
           <t>68.27476452672317</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1612</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1612.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39995,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40179,11 @@
           <t>15.86</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>16.93</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40230,16 @@
           <t>5816.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>2135.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>2135.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>2406.3</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>2973.86</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>2973.86</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40256,10 @@
           <t>155.8338220959245</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>5816</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>5816.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40425,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40609,11 @@
           <t>15.96</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>16.96</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40660,16 @@
           <t>796.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>1325.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>1325</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>1925.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>2912.66</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>2912.66</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40686,10 @@
           <t>-175.0758750229279</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>796</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>796.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40855,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41039,11 @@
           <t>16.01</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>16.46</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41090,16 @@
           <t>2223.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>2207.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>2207.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>1969.2</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>2984.7</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>2984.7</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41116,10 @@
           <t>-103.6941610847555</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>2223</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>2223.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41285,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41469,11 @@
           <t>16.12</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41520,16 @@
           <t>935.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>2025.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>2025</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>1934.8</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>3006.12</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>3006.12</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41546,10 @@
           <t>-150.9097782771964</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>935</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>935.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41715,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41899,11 @@
           <t>16.2</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>17.04</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41950,16 @@
           <t>908.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>2062.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>2062.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>1981.4</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>3040.84</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>3040.84</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41976,10 @@
           <t>-74.9710250422122</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>908</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>908.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42145,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42329,11 @@
           <t>16.29</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42380,16 @@
           <t>1763.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>2677.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>2677</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>2141.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>3096.62</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>3096.62</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42406,10 @@
           <t>39.08330190213019</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>1763</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>1763.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42575,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42759,11 @@
           <t>16.39</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>16.71</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>17.1</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42810,16 @@
           <t>5210.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>2526.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>2526.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>2151.2</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>3177.52</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>3177.52</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42836,10 @@
           <t>109.0150796118287</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>5210</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>5210.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43005,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43189,11 @@
           <t>16.5</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>17.12</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43240,16 @@
           <t>1309.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>1730.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>1730.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1853.9</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>3144.96</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>3144.96</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43266,10 @@
           <t>-164.297205074738</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>1309</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>1309.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43435,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43619,11 @@
           <t>16.49</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>16.79</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43670,16 @@
           <t>1124.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>1844.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>1844.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1896.8</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>3192.28</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>3192.28</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43696,10 @@
           <t>-130.9112830171648</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>1124</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>1124.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43865,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44049,11 @@
           <t>16.47</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>17.16</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44100,16 @@
           <t>3979.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>1900.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>1900</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>1928.7</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>3243.68</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>3243.68</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44126,10 @@
           <t>-58.72027711287592</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>3979</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>3979.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
